--- a/bonificacoes.xlsx
+++ b/bonificacoes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fabio\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{359FB329-8386-4C54-99D5-F7AAE3F540CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2E29327-1A5C-4DCF-BE0F-0AD56ED4AB9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{340A7D78-9F74-4795-B815-B0BCB910886D}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="10">
   <si>
     <t>Bruno fez sozinho</t>
   </si>
@@ -66,6 +66,9 @@
   </si>
   <si>
     <t>Instalação Geladeira</t>
+  </si>
+  <si>
+    <t>Alexandre</t>
   </si>
 </sst>
 </file>
@@ -456,7 +459,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27B7C978-5043-434E-A353-73395B78712F}">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultColWidth="4.3125" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="3.734375" style="1" customWidth="1"/>
@@ -641,6 +644,23 @@
         <v>3</v>
       </c>
     </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="1">
+        <v>8</v>
+      </c>
+      <c r="B11" s="4">
+        <v>45859</v>
+      </c>
+      <c r="C11" s="1">
+        <v>813</v>
+      </c>
+      <c r="D11" s="2">
+        <v>5</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/bonificacoes.xlsx
+++ b/bonificacoes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fabio\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2E29327-1A5C-4DCF-BE0F-0AD56ED4AB9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB1FD359-A29C-4280-B6B5-5AF8089F0C2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{340A7D78-9F74-4795-B815-B0BCB910886D}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="10">
   <si>
     <t>Bruno fez sozinho</t>
   </si>
@@ -459,7 +459,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27B7C978-5043-434E-A353-73395B78712F}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultColWidth="4.3125" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="3.734375" style="1" customWidth="1"/>
@@ -661,6 +661,40 @@
         <v>9</v>
       </c>
     </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="1">
+        <v>9</v>
+      </c>
+      <c r="B12" s="4">
+        <v>45863</v>
+      </c>
+      <c r="C12" s="1">
+        <v>853</v>
+      </c>
+      <c r="D12" s="2">
+        <v>5</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="1">
+        <v>10</v>
+      </c>
+      <c r="B13" s="4">
+        <v>45866</v>
+      </c>
+      <c r="C13" s="1">
+        <v>82981004247</v>
+      </c>
+      <c r="D13" s="2">
+        <v>250</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/bonificacoes.xlsx
+++ b/bonificacoes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fabio\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB1FD359-A29C-4280-B6B5-5AF8089F0C2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4F6694E-0ED8-48FA-AFF2-302BBA76C173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{340A7D78-9F74-4795-B815-B0BCB910886D}"/>
   </bookViews>
@@ -39,19 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="10">
-  <si>
-    <t>Bruno fez sozinho</t>
-  </si>
-  <si>
-    <t>Ronaldo</t>
-  </si>
-  <si>
-    <t>Bruno</t>
-  </si>
-  <si>
-    <t>Araujo</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Técnico</t>
   </si>
@@ -63,12 +51,6 @@
   </si>
   <si>
     <t>Data</t>
-  </si>
-  <si>
-    <t>Instalação Geladeira</t>
-  </si>
-  <si>
-    <t>Alexandre</t>
   </si>
 </sst>
 </file>
@@ -459,7 +441,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27B7C978-5043-434E-A353-73395B78712F}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultColWidth="4.3125" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="3.734375" style="1" customWidth="1"/>
@@ -471,229 +453,76 @@
     <col min="7" max="16384" width="4.3125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="4">
-        <v>45840</v>
-      </c>
-      <c r="C2" s="1">
-        <v>82981004292</v>
-      </c>
-      <c r="D2" s="2">
-        <v>250</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4">
-        <v>45840</v>
-      </c>
-      <c r="C3" s="1">
-        <v>82981004292</v>
-      </c>
-      <c r="D3" s="2">
-        <v>5</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4">
-        <v>45841</v>
-      </c>
-      <c r="C4" s="3">
-        <v>69531787</v>
-      </c>
-      <c r="D4" s="2">
-        <v>5</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4">
-        <v>45841</v>
-      </c>
-      <c r="C5" s="3">
-        <v>69642563</v>
-      </c>
-      <c r="D5" s="2">
-        <v>5</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="1">
-        <v>3</v>
-      </c>
-      <c r="B6" s="4">
-        <v>45841</v>
-      </c>
-      <c r="C6" s="3">
-        <v>69531787</v>
-      </c>
-      <c r="D6" s="2">
-        <v>5</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="1">
-        <v>4</v>
-      </c>
-      <c r="B7" s="4">
-        <v>45841</v>
-      </c>
-      <c r="C7" s="3">
-        <v>69642563</v>
-      </c>
-      <c r="D7" s="2">
-        <v>5</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="1">
-        <v>5</v>
-      </c>
-      <c r="B8" s="4">
-        <v>45841</v>
-      </c>
-      <c r="C8" s="3">
-        <v>82981004249</v>
-      </c>
-      <c r="D8" s="2">
-        <v>5</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="1">
-        <v>6</v>
-      </c>
-      <c r="B9" s="4">
-        <v>45841</v>
-      </c>
-      <c r="C9" s="3">
-        <v>82981004249</v>
-      </c>
-      <c r="D9" s="2">
-        <v>5</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="1">
-        <v>7</v>
-      </c>
-      <c r="B10" s="4">
-        <v>45840</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="2">
-        <v>250</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="1">
-        <v>8</v>
-      </c>
-      <c r="B11" s="4">
-        <v>45859</v>
-      </c>
-      <c r="C11" s="1">
-        <v>813</v>
-      </c>
-      <c r="D11" s="2">
-        <v>5</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="1">
-        <v>9</v>
-      </c>
-      <c r="B12" s="4">
-        <v>45863</v>
-      </c>
-      <c r="C12" s="1">
-        <v>853</v>
-      </c>
-      <c r="D12" s="2">
-        <v>5</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="1">
-        <v>10</v>
-      </c>
-      <c r="B13" s="4">
-        <v>45866</v>
-      </c>
-      <c r="C13" s="1">
-        <v>82981004247</v>
-      </c>
-      <c r="D13" s="2">
-        <v>250</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="B2" s="4"/>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B3" s="4"/>
+      <c r="D3" s="2"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B4" s="4"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="2"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B5" s="4"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B6" s="4"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B7" s="4"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B8" s="4"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="2"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B9" s="4"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B10" s="4"/>
+      <c r="D10" s="2"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B11" s="4"/>
+      <c r="D11" s="2"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" s="4"/>
+      <c r="D12" s="2"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B13" s="4"/>
+      <c r="D13" s="2"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>

--- a/bonificacoes.xlsx
+++ b/bonificacoes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fabio\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4F6694E-0ED8-48FA-AFF2-302BBA76C173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60C5DAB4-871C-4759-8AB0-8BC6DC92999D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{340A7D78-9F74-4795-B815-B0BCB910886D}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Técnico</t>
   </si>
@@ -51,6 +51,9 @@
   </si>
   <si>
     <t>Data</t>
+  </si>
+  <si>
+    <t>Alexandre</t>
   </si>
 </sst>
 </file>
@@ -471,8 +474,18 @@
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="D2" s="2"/>
+      <c r="B2" s="4">
+        <v>45873</v>
+      </c>
+      <c r="C2" s="1">
+        <v>850</v>
+      </c>
+      <c r="D2" s="2">
+        <v>5</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="4"/>

--- a/bonificacoes.xlsx
+++ b/bonificacoes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fabio\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60C5DAB4-871C-4759-8AB0-8BC6DC92999D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57BCC0A0-D08B-495B-BAF4-9AD14D7A07C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{340A7D78-9F74-4795-B815-B0BCB910886D}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
   <si>
     <t>Técnico</t>
   </si>
@@ -54,6 +54,18 @@
   </si>
   <si>
     <t>Alexandre</t>
+  </si>
+  <si>
+    <t>Araujo</t>
+  </si>
+  <si>
+    <t>Bruno</t>
+  </si>
+  <si>
+    <t>Jeferson</t>
+  </si>
+  <si>
+    <t>Adnré Francioli</t>
   </si>
 </sst>
 </file>
@@ -488,28 +500,89 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3" s="4"/>
-      <c r="D3" s="2"/>
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4">
+        <v>45874</v>
+      </c>
+      <c r="C3" s="1">
+        <v>69837964</v>
+      </c>
+      <c r="D3" s="2">
+        <v>250</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B4" s="4"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="2"/>
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4">
+        <v>45874</v>
+      </c>
+      <c r="C4" s="3">
+        <v>851</v>
+      </c>
+      <c r="D4" s="2">
+        <v>5</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B5" s="4"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="2"/>
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4">
+        <v>45876</v>
+      </c>
+      <c r="C5" s="3">
+        <v>879</v>
+      </c>
+      <c r="D5" s="2">
+        <v>5</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="4"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="2"/>
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4">
+        <v>45876</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2">
+        <v>5</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B7" s="4"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="2"/>
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4">
+        <v>45876</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="2">
+        <v>5</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" s="4"/>

--- a/bonificacoes.xlsx
+++ b/bonificacoes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fabio\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57BCC0A0-D08B-495B-BAF4-9AD14D7A07C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CA28A8C-B871-4E0B-B5BF-4455A8C18D21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{340A7D78-9F74-4795-B815-B0BCB910886D}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="9">
   <si>
     <t>Técnico</t>
   </si>
@@ -585,21 +585,56 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B8" s="4"/>
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4">
+        <v>45877</v>
+      </c>
       <c r="C8" s="3"/>
-      <c r="D8" s="2"/>
+      <c r="D8" s="2">
+        <v>250</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="4"/>
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4">
+        <v>45877</v>
+      </c>
       <c r="C9" s="3"/>
-      <c r="D9" s="2"/>
+      <c r="D9" s="2">
+        <v>250</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B10" s="4"/>
-      <c r="D10" s="2"/>
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4">
+        <v>45877</v>
+      </c>
+      <c r="D10" s="2">
+        <v>250</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B11" s="4"/>
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4">
+        <v>45877</v>
+      </c>
       <c r="D11" s="2"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">

--- a/bonificacoes.xlsx
+++ b/bonificacoes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fabio\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CA28A8C-B871-4E0B-B5BF-4455A8C18D21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A64AB92-B7F1-4F2B-8C01-0DC8903664D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{340A7D78-9F74-4795-B815-B0BCB910886D}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="11">
   <si>
     <t>Técnico</t>
   </si>
@@ -66,6 +66,12 @@
   </si>
   <si>
     <t>Adnré Francioli</t>
+  </si>
+  <si>
+    <t>Karen</t>
+  </si>
+  <si>
+    <t>Lucas Ribeiro Santana</t>
   </si>
 </sst>
 </file>
@@ -456,7 +462,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27B7C978-5043-434E-A353-73395B78712F}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultColWidth="4.3125" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="3.734375" style="1" customWidth="1"/>
@@ -630,23 +636,79 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" s="4">
         <v>45877</v>
       </c>
-      <c r="D11" s="2"/>
+      <c r="C11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="2">
+        <v>5</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="4"/>
-      <c r="D12" s="2"/>
+      <c r="A12" s="1">
+        <v>12</v>
+      </c>
+      <c r="B12" s="4">
+        <v>45877</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2">
+        <v>5</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B13" s="4"/>
-      <c r="D13" s="2"/>
+      <c r="A13" s="1">
+        <v>13</v>
+      </c>
+      <c r="B13" s="4">
+        <v>45881</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="2">
+        <v>5</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="1">
+        <v>14</v>
+      </c>
+      <c r="B14" s="4">
+        <v>45881</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="2">
+        <v>5</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <hyperlinks>
+    <hyperlink ref="C13" r:id="rId1" display="https://www.google.com/maps/contrib/110476760258098395637/reviews?hl=pt-BR" xr:uid="{27992953-7F91-467C-BC69-10B51EC9F80E}"/>
+    <hyperlink ref="C14" r:id="rId2" display="https://www.google.com/maps/contrib/110476760258098395637/reviews?hl=pt-BR" xr:uid="{190CA0F1-C66C-4BC5-A199-4742D8AC1C0A}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
--- a/bonificacoes.xlsx
+++ b/bonificacoes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fabio\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A64AB92-B7F1-4F2B-8C01-0DC8903664D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD72A5B4-9F86-4AEC-BF19-A3C281BF0CE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{340A7D78-9F74-4795-B815-B0BCB910886D}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="16">
   <si>
     <t>Técnico</t>
   </si>
@@ -72,6 +72,21 @@
   </si>
   <si>
     <t>Lucas Ribeiro Santana</t>
+  </si>
+  <si>
+    <t>Ryan Amaral</t>
+  </si>
+  <si>
+    <t>Vinicius Cirilo</t>
+  </si>
+  <si>
+    <t>Aline O Reis</t>
+  </si>
+  <si>
+    <t>Carlos Henrique</t>
+  </si>
+  <si>
+    <t>Shopping D&amp;D</t>
   </si>
 </sst>
 </file>
@@ -462,7 +477,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27B7C978-5043-434E-A353-73395B78712F}">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultColWidth="4.3125" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="3.734375" style="1" customWidth="1"/>
@@ -702,13 +717,138 @@
         <v>7</v>
       </c>
     </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="1">
+        <v>15</v>
+      </c>
+      <c r="B15" s="4">
+        <v>45882</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="2">
+        <v>5</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="1">
+        <v>16</v>
+      </c>
+      <c r="B16" s="4">
+        <v>45882</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="2">
+        <v>5</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="1">
+        <v>17</v>
+      </c>
+      <c r="B17" s="4">
+        <v>45882</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="2">
+        <v>5</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="1">
+        <v>18</v>
+      </c>
+      <c r="B18" s="4">
+        <v>45884</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="2">
+        <v>5</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="1">
+        <v>19</v>
+      </c>
+      <c r="B19" s="4">
+        <v>45887</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="2">
+        <v>5</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="1">
+        <v>20</v>
+      </c>
+      <c r="B20" s="4">
+        <v>45887</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" s="2">
+        <v>5</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="1">
+        <v>21</v>
+      </c>
+      <c r="B21" s="4">
+        <v>45889</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="2">
+        <v>100</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <hyperlinks>
     <hyperlink ref="C13" r:id="rId1" display="https://www.google.com/maps/contrib/110476760258098395637/reviews?hl=pt-BR" xr:uid="{27992953-7F91-467C-BC69-10B51EC9F80E}"/>
     <hyperlink ref="C14" r:id="rId2" display="https://www.google.com/maps/contrib/110476760258098395637/reviews?hl=pt-BR" xr:uid="{190CA0F1-C66C-4BC5-A199-4742D8AC1C0A}"/>
+    <hyperlink ref="C15" r:id="rId3" display="https://www.google.com/maps/contrib/109019119608432970477/reviews?hl=pt-BR" xr:uid="{3E712B97-89AC-4B7E-A18B-E9E96E534977}"/>
+    <hyperlink ref="C16" r:id="rId4" display="https://www.google.com/maps/contrib/101581825414658169568/reviews?hl=pt-BR" xr:uid="{4D502781-8677-433A-8261-8F1947CA5403}"/>
+    <hyperlink ref="C17" r:id="rId5" display="https://www.google.com/maps/contrib/101581825414658169568/reviews?hl=pt-BR" xr:uid="{79DE4F31-5AC2-488D-9E61-9E10DA1A4A24}"/>
+    <hyperlink ref="C18" r:id="rId6" display="https://www.google.com/maps/contrib/104672967878640650642/reviews?hl=pt-BR" xr:uid="{880FEB5E-9717-41CE-B6FD-5BF847669E31}"/>
+    <hyperlink ref="C19" r:id="rId7" display="https://www.google.com/maps/contrib/110295289811600012353/reviews?hl=pt-BR" xr:uid="{6B32ACC9-8739-4498-B2C4-0DD572878A46}"/>
+    <hyperlink ref="C20" r:id="rId8" display="https://www.google.com/maps/contrib/110295289811600012353/reviews?hl=pt-BR" xr:uid="{C99B0DF9-64D0-43EC-A987-27BEC2A25DF5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId9"/>
 </worksheet>
 </file>